--- a/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDOrganizationAbteilung.xlsx
+++ b/r5-ELGA-MOPED-256-Beispiele-für-maskierte-Ressourcen-erstellen/StructureDefinition-MOPEDOrganizationAbteilung.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T14:27:25+00:00</t>
+    <t>2024-11-11T10:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -512,7 +512,7 @@
     <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:type.coding.code}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
@@ -636,13 +636,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="Funktionscode"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -674,6 +667,9 @@
   </si>
   <si>
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://example.org/lkf-system/funktionscode</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -809,14 +805,10 @@
     <t>Organization.identifier:Funktionssubcode.type</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="Funktionssubcode"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>Organization.identifier:Funktionssubcode.system</t>
+  </si>
+  <si>
+    <t>http://example.org/lkf-system/funktionssubcode</t>
   </si>
   <si>
     <t>Organization.identifier:Funktionssubcode.value</t>
@@ -1437,7 +1429,7 @@
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.734375" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3373,49 +3365,49 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="S17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AA17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3433,7 +3425,7 @@
         <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>191</v>
@@ -3447,10 +3439,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3458,7 +3450,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
@@ -3476,23 +3468,23 @@
         <v>102</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>19</v>
@@ -4430,7 +4422,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>254</v>
+        <v>19</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>19</v>
@@ -4448,31 +4440,31 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4490,7 +4482,7 @@
         <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>191</v>
@@ -4504,10 +4496,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4515,7 +4507,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4533,23 +4525,23 @@
         <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>19</v>
